--- a/Smart Dashboard - 19 Punjab.xlsx
+++ b/Smart Dashboard - 19 Punjab.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D_Main\training\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB892047-8237-4633-B57C-EE61069462C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2B0D31-BC4C-48E1-892E-95FEE06DC4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2032,29 +2032,6 @@
   </cellStyleXfs>
   <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2155,6 +2132,29 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2436,277 +2436,277 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
     </row>
     <row r="5" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="3">
         <v>750</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="3">
         <v>310</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="4">
         <f t="shared" ref="D6:D12" si="0">IF(B6=0,0,C6/B6)</f>
         <v>0.41333333333333333</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="5">
         <v>0.3</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="4">
         <f t="shared" ref="F6:F12" si="1">D6*E6</f>
         <v>0.124</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="3">
         <v>44</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="3">
         <v>31</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="4">
         <f t="shared" si="0"/>
         <v>0.70454545454545459</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="5">
         <v>0.25</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="4">
         <f t="shared" si="1"/>
         <v>0.17613636363636365</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="3">
         <v>65</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="3">
         <v>48</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="4">
         <f t="shared" si="0"/>
         <v>0.7384615384615385</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="5">
         <v>0.1</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="4">
         <f t="shared" si="1"/>
         <v>7.3846153846153853E-2</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="3">
         <v>680</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="3">
         <v>590</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="4">
         <f t="shared" si="0"/>
         <v>0.86764705882352944</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="5">
         <v>0.15</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="4">
         <f t="shared" si="1"/>
         <v>0.13014705882352942</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="3">
         <v>95</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="3">
         <v>78</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="4">
         <f t="shared" si="0"/>
         <v>0.82105263157894737</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="5">
         <v>0.1</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="4">
         <f t="shared" si="1"/>
         <v>8.2105263157894737E-2</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="3">
         <v>180</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="3">
         <v>142</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="4">
         <f t="shared" si="0"/>
         <v>0.78888888888888886</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="5">
         <v>0.05</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="4">
         <f t="shared" si="1"/>
         <v>3.9444444444444449E-2</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="3">
         <v>95</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="3">
         <v>81</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="4">
         <f t="shared" si="0"/>
         <v>0.85263157894736841</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="5">
         <v>0.05</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="4">
         <f t="shared" si="1"/>
         <v>4.2631578947368423E-2</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="17">
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8">
         <f>SUM(F6:F12)</f>
         <v>0.66831086285575447</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
     </row>
     <row r="17" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="10">
         <v>750</v>
       </c>
       <c r="C18" t="s">
@@ -2720,17 +2720,17 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="12">
         <v>540</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="13">
         <f>B19/B18</f>
         <v>0.72</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="13">
         <f>B19/B18</f>
         <v>0.72</v>
       </c>
@@ -2739,195 +2739,195 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="3">
         <v>40</v>
       </c>
-      <c r="C20" s="13">
+      <c r="C20" s="4">
         <f t="shared" ref="C20:C26" si="2">B20/$B$19</f>
         <v>7.407407407407407E-2</v>
       </c>
-      <c r="D20" s="13">
+      <c r="D20" s="4">
         <f t="shared" ref="D20:D26" si="3">B20/$B$18</f>
         <v>5.3333333333333337E-2</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="3">
         <v>25</v>
       </c>
-      <c r="C21" s="13">
+      <c r="C21" s="4">
         <f t="shared" si="2"/>
         <v>4.6296296296296294E-2</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="4">
         <f t="shared" si="3"/>
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="3">
         <v>55</v>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="4">
         <f t="shared" si="2"/>
         <v>0.10185185185185185</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="4">
         <f t="shared" si="3"/>
         <v>7.3333333333333334E-2</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="3">
         <v>35</v>
       </c>
-      <c r="C23" s="13">
+      <c r="C23" s="4">
         <f t="shared" si="2"/>
         <v>6.4814814814814811E-2</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="4">
         <f t="shared" si="3"/>
         <v>4.6666666666666669E-2</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="3">
         <v>30</v>
       </c>
-      <c r="C24" s="13">
+      <c r="C24" s="4">
         <f t="shared" si="2"/>
         <v>5.5555555555555552E-2</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="4">
         <f t="shared" si="3"/>
         <v>0.04</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="3">
         <v>45</v>
       </c>
-      <c r="C25" s="13">
+      <c r="C25" s="4">
         <f t="shared" si="2"/>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="4">
         <f t="shared" si="3"/>
         <v>0.06</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="16">
         <v>310</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="17">
         <f t="shared" si="2"/>
         <v>0.57407407407407407</v>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="17">
         <f t="shared" si="3"/>
         <v>0.41333333333333333</v>
       </c>
-      <c r="E26" s="25" t="s">
+      <c r="E26" s="16" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="27">
+      <c r="B27" s="18">
         <f>SUM(B20:B26)</f>
         <v>540</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="30">
+      <c r="B29" s="21">
         <f>B18-B19</f>
         <v>210</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="22">
         <f>B29/B18</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30" t="s">
+      <c r="D29" s="21"/>
+      <c r="E29" s="21" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
+      <c r="A32" s="48"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
+      <c r="A33" s="48"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2961,286 +2961,286 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="46" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
     </row>
     <row r="4" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="3">
         <v>210</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="3">
         <v>95</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="3">
         <v>40</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="35">
         <v>28</v>
       </c>
-      <c r="F5" s="41">
+      <c r="F5" s="32">
         <v>15</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="23" t="s">
         <v>250</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="I5" s="32" t="s">
+      <c r="I5" s="23" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="3">
         <v>85</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="3">
         <v>55</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="3">
         <v>38</v>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="35">
         <v>22</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="32">
         <v>12</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="I6" s="32" t="s">
+      <c r="I6" s="23" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="3">
         <v>72</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="3">
         <v>48</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="3">
         <v>35</v>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="35">
         <v>18</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="32">
         <v>10</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="23" t="s">
         <v>258</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="I7" s="32" t="s">
+      <c r="I7" s="23" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="3">
         <v>58</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="3">
         <v>42</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="3">
         <v>30</v>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="35">
         <v>14</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="32">
         <v>8</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="23" t="s">
         <v>262</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="I8" s="32" t="s">
+      <c r="I8" s="23" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="3">
         <v>28</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="3">
         <v>22</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="3">
         <v>18</v>
       </c>
-      <c r="E9" s="44">
+      <c r="E9" s="35">
         <v>9</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="32">
         <v>5</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="23" t="s">
         <v>266</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="I9" s="32" t="s">
+      <c r="I9" s="23" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="3">
         <v>18</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="3">
         <v>15</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="3">
         <v>12</v>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="35">
         <v>4</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="32">
         <v>2</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="23" t="s">
         <v>270</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="I10" s="32" t="s">
+      <c r="I10" s="23" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="18">
         <f>SUM(B5:B10)</f>
         <v>471</v>
       </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="48" t="s">
         <v>274</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
+      <c r="A15" s="48"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3272,358 +3272,358 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="4" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="49">
+      <c r="A5" s="40">
         <v>1</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="42" t="s">
         <v>283</v>
       </c>
-      <c r="D5" s="49" t="s">
+      <c r="D5" s="40" t="s">
         <v>284</v>
       </c>
-      <c r="E5" s="49" t="s">
+      <c r="E5" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="F5" s="51" t="s">
+      <c r="F5" s="42" t="s">
         <v>286</v>
       </c>
-      <c r="G5" s="49" t="s">
+      <c r="G5" s="40" t="s">
         <v>287</v>
       </c>
-      <c r="H5" s="51" t="s">
+      <c r="H5" s="42" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="49">
+      <c r="A6" s="40">
         <v>2</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="41" t="s">
         <v>289</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="40" t="s">
         <v>291</v>
       </c>
-      <c r="E6" s="49" t="s">
+      <c r="E6" s="40" t="s">
         <v>292</v>
       </c>
-      <c r="F6" s="51" t="s">
+      <c r="F6" s="42" t="s">
         <v>293</v>
       </c>
-      <c r="G6" s="49" t="s">
+      <c r="G6" s="40" t="s">
         <v>294</v>
       </c>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="42" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="23" t="s">
         <v>300</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="H7" s="32" t="s">
+      <c r="H7" s="23" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="23" t="s">
         <v>307</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="23" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="23" t="s">
         <v>311</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="23" t="s">
         <v>314</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="23" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="12">
+      <c r="A10" s="3">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="23" t="s">
         <v>318</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="H10" s="32" t="s">
+      <c r="H10" s="23" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="12">
+      <c r="A11" s="3">
         <v>7</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="23" t="s">
         <v>325</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="F11" s="23" t="s">
         <v>328</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="H11" s="32"/>
+      <c r="H11" s="23"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="12">
+      <c r="A12" s="3">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="23" t="s">
         <v>331</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="F12" s="23" t="s">
         <v>334</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="H12" s="32"/>
+      <c r="H12" s="23"/>
     </row>
     <row r="13" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="12">
+      <c r="A13" s="3">
         <v>9</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="23" t="s">
         <v>337</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="F13" s="23" t="s">
         <v>340</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="H13" s="32" t="s">
+      <c r="H13" s="23" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="12">
+      <c r="A14" s="3">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="23" t="s">
         <v>344</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="23" t="s">
         <v>347</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="H14" s="32" t="s">
+      <c r="H14" s="23" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="12">
+      <c r="A15" s="3">
         <v>11</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="23" t="s">
         <v>351</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="F15" s="23" t="s">
         <v>354</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="H15" s="32" t="s">
+      <c r="H15" s="23" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="52" t="s">
         <v>357</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="A18" s="52"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3653,614 +3653,614 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="46" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="4" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="49">
+      <c r="A5" s="40">
         <v>1</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="41" t="s">
         <v>362</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="42" t="s">
         <v>363</v>
       </c>
-      <c r="D5" s="49" t="s">
+      <c r="D5" s="40" t="s">
         <v>364</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="42" t="s">
         <v>365</v>
       </c>
-      <c r="F5" s="49" t="s">
+      <c r="F5" s="40" t="s">
         <v>366</v>
       </c>
-      <c r="G5" s="51" t="s">
+      <c r="G5" s="42" t="s">
         <v>367</v>
       </c>
-      <c r="H5" s="51" t="s">
+      <c r="H5" s="42" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="23" t="s">
         <v>370</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="23" t="s">
         <v>372</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="23" t="s">
         <v>373</v>
       </c>
-      <c r="H6" s="32"/>
+      <c r="H6" s="23"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="49">
+      <c r="A7" s="40">
         <v>3</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="41" t="s">
         <v>374</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="42" t="s">
         <v>375</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="40" t="s">
         <v>376</v>
       </c>
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="42" t="s">
         <v>365</v>
       </c>
-      <c r="F7" s="49" t="s">
+      <c r="F7" s="40" t="s">
         <v>320</v>
       </c>
-      <c r="G7" s="51" t="s">
+      <c r="G7" s="42" t="s">
         <v>377</v>
       </c>
-      <c r="H7" s="51" t="s">
+      <c r="H7" s="42" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="23" t="s">
         <v>380</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="23" t="s">
         <v>382</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="23" t="s">
         <v>383</v>
       </c>
-      <c r="H8" s="32"/>
+      <c r="H8" s="23"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="23" t="s">
         <v>385</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="E9" s="23" t="s">
         <v>382</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="23" t="s">
         <v>388</v>
       </c>
-      <c r="H9" s="32"/>
+      <c r="H9" s="23"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="12">
+      <c r="A10" s="3">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="23" t="s">
         <v>390</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="23" t="s">
         <v>365</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="23" t="s">
         <v>392</v>
       </c>
-      <c r="H10" s="32"/>
+      <c r="H10" s="23"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="12">
+      <c r="A11" s="3">
         <v>7</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="23" t="s">
         <v>394</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="23" t="s">
         <v>396</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="G11" s="32" t="s">
+      <c r="G11" s="23" t="s">
         <v>398</v>
       </c>
-      <c r="H11" s="32"/>
+      <c r="H11" s="23"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="12">
+      <c r="A12" s="3">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="23" t="s">
         <v>400</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="23" t="s">
         <v>365</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="23" t="s">
         <v>402</v>
       </c>
-      <c r="H12" s="32"/>
+      <c r="H12" s="23"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="12">
+      <c r="A13" s="3">
         <v>9</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="23" t="s">
         <v>404</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="23" t="s">
         <v>406</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="23" t="s">
         <v>407</v>
       </c>
-      <c r="H13" s="32"/>
+      <c r="H13" s="23"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="12">
+      <c r="A14" s="3">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="23" t="s">
         <v>409</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="23" t="s">
         <v>309</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="23" t="s">
         <v>411</v>
       </c>
-      <c r="H14" s="32"/>
+      <c r="H14" s="23"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="12">
+      <c r="A15" s="3">
         <v>11</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="23" t="s">
         <v>413</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="23" t="s">
         <v>415</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="G15" s="32" t="s">
+      <c r="G15" s="23" t="s">
         <v>416</v>
       </c>
-      <c r="H15" s="32"/>
+      <c r="H15" s="23"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="12">
+      <c r="A16" s="3">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="23" t="s">
         <v>418</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="23" t="s">
         <v>420</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="23" t="s">
         <v>416</v>
       </c>
-      <c r="H16" s="32"/>
+      <c r="H16" s="23"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="12">
+      <c r="A17" s="3">
         <v>13</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="23" t="s">
         <v>422</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="23" t="s">
         <v>424</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="G17" s="32" t="s">
+      <c r="G17" s="23" t="s">
         <v>416</v>
       </c>
-      <c r="H17" s="32"/>
+      <c r="H17" s="23"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="12">
+      <c r="A18" s="3">
         <v>14</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="23" t="s">
         <v>426</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="E18" s="32" t="s">
+      <c r="E18" s="23" t="s">
         <v>428</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="23" t="s">
         <v>429</v>
       </c>
-      <c r="H18" s="32"/>
+      <c r="H18" s="23"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="12">
+      <c r="A19" s="3">
         <v>15</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C19" s="23" t="s">
         <v>431</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="23" t="s">
         <v>415</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G19" s="32" t="s">
+      <c r="G19" s="23" t="s">
         <v>433</v>
       </c>
-      <c r="H19" s="32"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="12">
+      <c r="A20" s="3">
         <v>16</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="23" t="s">
         <v>435</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="E20" s="23" t="s">
         <v>420</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="23" t="s">
         <v>433</v>
       </c>
-      <c r="H20" s="32"/>
+      <c r="H20" s="23"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="12">
+      <c r="A21" s="3">
         <v>17</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="23" t="s">
         <v>438</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="E21" s="32" t="s">
+      <c r="E21" s="23" t="s">
         <v>424</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="G21" s="32" t="s">
+      <c r="G21" s="23" t="s">
         <v>433</v>
       </c>
-      <c r="H21" s="32"/>
+      <c r="H21" s="23"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="12">
+      <c r="A22" s="3">
         <v>18</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="23" t="s">
         <v>441</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="E22" s="32" t="s">
+      <c r="E22" s="23" t="s">
         <v>428</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F22" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="G22" s="32" t="s">
+      <c r="G22" s="23" t="s">
         <v>443</v>
       </c>
-      <c r="H22" s="32"/>
+      <c r="H22" s="23"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="49">
+      <c r="A23" s="40">
         <v>19</v>
       </c>
-      <c r="B23" s="50" t="s">
+      <c r="B23" s="41" t="s">
         <v>444</v>
       </c>
-      <c r="C23" s="51" t="s">
+      <c r="C23" s="42" t="s">
         <v>445</v>
       </c>
-      <c r="D23" s="49" t="s">
+      <c r="D23" s="40" t="s">
         <v>446</v>
       </c>
-      <c r="E23" s="51" t="s">
+      <c r="E23" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="F23" s="49" t="s">
+      <c r="F23" s="40" t="s">
         <v>447</v>
       </c>
-      <c r="G23" s="51" t="s">
+      <c r="G23" s="42" t="s">
         <v>448</v>
       </c>
-      <c r="H23" s="51" t="s">
+      <c r="H23" s="42" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="49">
+      <c r="A24" s="40">
         <v>20</v>
       </c>
-      <c r="B24" s="50" t="s">
+      <c r="B24" s="41" t="s">
         <v>450</v>
       </c>
-      <c r="C24" s="51" t="s">
+      <c r="C24" s="42" t="s">
         <v>451</v>
       </c>
-      <c r="D24" s="49" t="s">
+      <c r="D24" s="40" t="s">
         <v>452</v>
       </c>
-      <c r="E24" s="51" t="s">
+      <c r="E24" s="42" t="s">
         <v>420</v>
       </c>
-      <c r="F24" s="49" t="s">
+      <c r="F24" s="40" t="s">
         <v>397</v>
       </c>
-      <c r="G24" s="51" t="s">
+      <c r="G24" s="42" t="s">
         <v>448</v>
       </c>
-      <c r="H24" s="51"/>
+      <c r="H24" s="42"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="49">
+      <c r="A25" s="40">
         <v>21</v>
       </c>
-      <c r="B25" s="50" t="s">
+      <c r="B25" s="41" t="s">
         <v>453</v>
       </c>
-      <c r="C25" s="51" t="s">
+      <c r="C25" s="42" t="s">
         <v>454</v>
       </c>
-      <c r="D25" s="49" t="s">
+      <c r="D25" s="40" t="s">
         <v>455</v>
       </c>
-      <c r="E25" s="51" t="s">
+      <c r="E25" s="42" t="s">
         <v>424</v>
       </c>
-      <c r="F25" s="49" t="s">
+      <c r="F25" s="40" t="s">
         <v>333</v>
       </c>
-      <c r="G25" s="51" t="s">
+      <c r="G25" s="42" t="s">
         <v>456</v>
       </c>
-      <c r="H25" s="51" t="s">
+      <c r="H25" s="42" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="49">
+      <c r="A26" s="40">
         <v>22</v>
       </c>
-      <c r="B26" s="50" t="s">
+      <c r="B26" s="41" t="s">
         <v>458</v>
       </c>
-      <c r="C26" s="51" t="s">
+      <c r="C26" s="42" t="s">
         <v>459</v>
       </c>
-      <c r="D26" s="49" t="s">
+      <c r="D26" s="40" t="s">
         <v>460</v>
       </c>
-      <c r="E26" s="51" t="s">
+      <c r="E26" s="42" t="s">
         <v>428</v>
       </c>
-      <c r="F26" s="49" t="s">
+      <c r="F26" s="40" t="s">
         <v>461</v>
       </c>
-      <c r="G26" s="51" t="s">
+      <c r="G26" s="42" t="s">
         <v>462</v>
       </c>
-      <c r="H26" s="51" t="s">
+      <c r="H26" s="42" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="52" t="s">
         <v>464</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
+      <c r="A29" s="52"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4296,1202 +4296,1202 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="46" t="s">
         <v>465</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="47" t="s">
         <v>466</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
     </row>
     <row r="4" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="52">
+      <c r="A5" s="43">
         <v>1</v>
       </c>
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="43" t="s">
         <v>475</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="43" t="s">
         <v>476</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="D5" s="44" t="s">
         <v>477</v>
       </c>
-      <c r="E5" s="52" t="s">
+      <c r="E5" s="43" t="s">
         <v>424</v>
       </c>
-      <c r="F5" s="53" t="s">
+      <c r="F5" s="44" t="s">
         <v>478</v>
       </c>
-      <c r="G5" s="53" t="s">
+      <c r="G5" s="44" t="s">
         <v>479</v>
       </c>
-      <c r="H5" s="53" t="s">
+      <c r="H5" s="44" t="s">
         <v>480</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="43">
         <v>13.9</v>
       </c>
-      <c r="J5" s="53" t="s">
+      <c r="J5" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K5" s="53" t="s">
+      <c r="K5" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="L5" s="53"/>
+      <c r="L5" s="44"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="52">
+      <c r="A6" s="43">
         <v>2</v>
       </c>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="43" t="s">
         <v>482</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="43" t="s">
         <v>476</v>
       </c>
-      <c r="D6" s="53" t="s">
+      <c r="D6" s="44" t="s">
         <v>483</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="43" t="s">
         <v>415</v>
       </c>
-      <c r="F6" s="53" t="s">
+      <c r="F6" s="44" t="s">
         <v>484</v>
       </c>
-      <c r="G6" s="53" t="s">
+      <c r="G6" s="44" t="s">
         <v>485</v>
       </c>
-      <c r="H6" s="53" t="s">
+      <c r="H6" s="44" t="s">
         <v>486</v>
       </c>
-      <c r="I6" s="52">
+      <c r="I6" s="43">
         <v>6.1</v>
       </c>
-      <c r="J6" s="54" t="s">
+      <c r="J6" s="45" t="s">
         <v>487</v>
       </c>
-      <c r="K6" s="53" t="s">
+      <c r="K6" s="44" t="s">
         <v>488</v>
       </c>
-      <c r="L6" s="53" t="s">
+      <c r="L6" s="44" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="52">
+      <c r="A7" s="43">
         <v>3</v>
       </c>
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="43" t="s">
         <v>490</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="43" t="s">
         <v>476</v>
       </c>
-      <c r="D7" s="53" t="s">
+      <c r="D7" s="44" t="s">
         <v>491</v>
       </c>
-      <c r="E7" s="52" t="s">
+      <c r="E7" s="43" t="s">
         <v>372</v>
       </c>
-      <c r="F7" s="53" t="s">
+      <c r="F7" s="44" t="s">
         <v>492</v>
       </c>
-      <c r="G7" s="53" t="s">
+      <c r="G7" s="44" t="s">
         <v>479</v>
       </c>
-      <c r="H7" s="53" t="s">
+      <c r="H7" s="44" t="s">
         <v>493</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7" s="43">
         <v>11.6</v>
       </c>
-      <c r="J7" s="54" t="s">
+      <c r="J7" s="45" t="s">
         <v>494</v>
       </c>
-      <c r="K7" s="53" t="s">
+      <c r="K7" s="44" t="s">
         <v>488</v>
       </c>
-      <c r="L7" s="53" t="s">
+      <c r="L7" s="44" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="52">
+      <c r="A8" s="43">
         <v>4</v>
       </c>
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="43" t="s">
         <v>495</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="43" t="s">
         <v>476</v>
       </c>
-      <c r="D8" s="53" t="s">
+      <c r="D8" s="44" t="s">
         <v>496</v>
       </c>
-      <c r="E8" s="52" t="s">
+      <c r="E8" s="43" t="s">
         <v>424</v>
       </c>
-      <c r="F8" s="53" t="s">
+      <c r="F8" s="44" t="s">
         <v>497</v>
       </c>
-      <c r="G8" s="53" t="s">
+      <c r="G8" s="44" t="s">
         <v>479</v>
       </c>
-      <c r="H8" s="53" t="s">
+      <c r="H8" s="44" t="s">
         <v>486</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8" s="43">
         <v>17.3</v>
       </c>
-      <c r="J8" s="53" t="s">
+      <c r="J8" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K8" s="53" t="s">
+      <c r="K8" s="44" t="s">
         <v>498</v>
       </c>
-      <c r="L8" s="53"/>
+      <c r="L8" s="44"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="52">
+      <c r="A9" s="43">
         <v>5</v>
       </c>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="43" t="s">
         <v>499</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="43" t="s">
         <v>476</v>
       </c>
-      <c r="D9" s="53" t="s">
+      <c r="D9" s="44" t="s">
         <v>500</v>
       </c>
-      <c r="E9" s="52" t="s">
+      <c r="E9" s="43" t="s">
         <v>424</v>
       </c>
-      <c r="F9" s="53" t="s">
+      <c r="F9" s="44" t="s">
         <v>501</v>
       </c>
-      <c r="G9" s="53" t="s">
+      <c r="G9" s="44" t="s">
         <v>502</v>
       </c>
-      <c r="H9" s="53" t="s">
+      <c r="H9" s="44" t="s">
         <v>503</v>
       </c>
-      <c r="I9" s="52">
+      <c r="I9" s="43">
         <v>15</v>
       </c>
-      <c r="J9" s="53" t="s">
+      <c r="J9" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K9" s="53" t="s">
+      <c r="K9" s="44" t="s">
         <v>504</v>
       </c>
-      <c r="L9" s="53"/>
+      <c r="L9" s="44"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="52">
+      <c r="A10" s="43">
         <v>6</v>
       </c>
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="43" t="s">
         <v>505</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="43" t="s">
         <v>476</v>
       </c>
-      <c r="D10" s="53" t="s">
+      <c r="D10" s="44" t="s">
         <v>506</v>
       </c>
-      <c r="E10" s="52" t="s">
+      <c r="E10" s="43" t="s">
         <v>415</v>
       </c>
-      <c r="F10" s="53" t="s">
+      <c r="F10" s="44" t="s">
         <v>507</v>
       </c>
-      <c r="G10" s="53" t="s">
+      <c r="G10" s="44" t="s">
         <v>508</v>
       </c>
-      <c r="H10" s="53" t="s">
+      <c r="H10" s="44" t="s">
         <v>509</v>
       </c>
-      <c r="I10" s="52">
+      <c r="I10" s="43">
         <v>12.1</v>
       </c>
-      <c r="J10" s="54" t="s">
+      <c r="J10" s="45" t="s">
         <v>494</v>
       </c>
-      <c r="K10" s="53" t="s">
+      <c r="K10" s="44" t="s">
         <v>510</v>
       </c>
-      <c r="L10" s="53" t="s">
+      <c r="L10" s="44" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="52">
+      <c r="A11" s="43">
         <v>7</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="43" t="s">
         <v>511</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="43" t="s">
         <v>476</v>
       </c>
-      <c r="D11" s="53" t="s">
+      <c r="D11" s="44" t="s">
         <v>491</v>
       </c>
-      <c r="E11" s="52" t="s">
+      <c r="E11" s="43" t="s">
         <v>415</v>
       </c>
-      <c r="F11" s="53" t="s">
+      <c r="F11" s="44" t="s">
         <v>478</v>
       </c>
-      <c r="G11" s="53" t="s">
+      <c r="G11" s="44" t="s">
         <v>508</v>
       </c>
-      <c r="H11" s="53" t="s">
+      <c r="H11" s="44" t="s">
         <v>512</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11" s="43">
         <v>15.8</v>
       </c>
-      <c r="J11" s="54" t="s">
+      <c r="J11" s="45" t="s">
         <v>494</v>
       </c>
-      <c r="K11" s="53" t="s">
+      <c r="K11" s="44" t="s">
         <v>498</v>
       </c>
-      <c r="L11" s="53" t="s">
+      <c r="L11" s="44" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="52">
+      <c r="A12" s="43">
         <v>8</v>
       </c>
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="43" t="s">
         <v>513</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="43" t="s">
         <v>476</v>
       </c>
-      <c r="D12" s="53" t="s">
+      <c r="D12" s="44" t="s">
         <v>514</v>
       </c>
-      <c r="E12" s="52" t="s">
+      <c r="E12" s="43" t="s">
         <v>424</v>
       </c>
-      <c r="F12" s="53" t="s">
+      <c r="F12" s="44" t="s">
         <v>515</v>
       </c>
-      <c r="G12" s="53" t="s">
+      <c r="G12" s="44" t="s">
         <v>508</v>
       </c>
-      <c r="H12" s="53" t="s">
+      <c r="H12" s="44" t="s">
         <v>516</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I12" s="43">
         <v>5.7</v>
       </c>
-      <c r="J12" s="53" t="s">
+      <c r="J12" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K12" s="53" t="s">
+      <c r="K12" s="44" t="s">
         <v>498</v>
       </c>
-      <c r="L12" s="53"/>
+      <c r="L12" s="44"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="52">
+      <c r="A13" s="43">
         <v>9</v>
       </c>
-      <c r="B13" s="52" t="s">
+      <c r="B13" s="43" t="s">
         <v>517</v>
       </c>
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="43" t="s">
         <v>476</v>
       </c>
-      <c r="D13" s="53" t="s">
+      <c r="D13" s="44" t="s">
         <v>518</v>
       </c>
-      <c r="E13" s="52" t="s">
+      <c r="E13" s="43" t="s">
         <v>420</v>
       </c>
-      <c r="F13" s="53" t="s">
+      <c r="F13" s="44" t="s">
         <v>515</v>
       </c>
-      <c r="G13" s="53" t="s">
+      <c r="G13" s="44" t="s">
         <v>519</v>
       </c>
-      <c r="H13" s="53" t="s">
+      <c r="H13" s="44" t="s">
         <v>520</v>
       </c>
-      <c r="I13" s="52">
+      <c r="I13" s="43">
         <v>6.7</v>
       </c>
-      <c r="J13" s="53" t="s">
+      <c r="J13" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K13" s="53" t="s">
+      <c r="K13" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="L13" s="53"/>
+      <c r="L13" s="44"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="52">
+      <c r="A14" s="43">
         <v>10</v>
       </c>
-      <c r="B14" s="52" t="s">
+      <c r="B14" s="43" t="s">
         <v>521</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="43" t="s">
         <v>476</v>
       </c>
-      <c r="D14" s="53" t="s">
+      <c r="D14" s="44" t="s">
         <v>522</v>
       </c>
-      <c r="E14" s="52" t="s">
+      <c r="E14" s="43" t="s">
         <v>415</v>
       </c>
-      <c r="F14" s="53" t="s">
+      <c r="F14" s="44" t="s">
         <v>478</v>
       </c>
-      <c r="G14" s="53" t="s">
+      <c r="G14" s="44" t="s">
         <v>485</v>
       </c>
-      <c r="H14" s="53" t="s">
+      <c r="H14" s="44" t="s">
         <v>516</v>
       </c>
-      <c r="I14" s="52">
+      <c r="I14" s="43">
         <v>8.6999999999999993</v>
       </c>
-      <c r="J14" s="53" t="s">
+      <c r="J14" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K14" s="53" t="s">
+      <c r="K14" s="44" t="s">
         <v>523</v>
       </c>
-      <c r="L14" s="53"/>
+      <c r="L14" s="44"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="52">
+      <c r="A15" s="43">
         <v>11</v>
       </c>
-      <c r="B15" s="52" t="s">
+      <c r="B15" s="43" t="s">
         <v>524</v>
       </c>
-      <c r="C15" s="52" t="s">
+      <c r="C15" s="43" t="s">
         <v>476</v>
       </c>
-      <c r="D15" s="53" t="s">
+      <c r="D15" s="44" t="s">
         <v>525</v>
       </c>
-      <c r="E15" s="52" t="s">
+      <c r="E15" s="43" t="s">
         <v>428</v>
       </c>
-      <c r="F15" s="53" t="s">
+      <c r="F15" s="44" t="s">
         <v>526</v>
       </c>
-      <c r="G15" s="53" t="s">
+      <c r="G15" s="44" t="s">
         <v>527</v>
       </c>
-      <c r="H15" s="53" t="s">
+      <c r="H15" s="44" t="s">
         <v>493</v>
       </c>
-      <c r="I15" s="52">
+      <c r="I15" s="43">
         <v>4.7</v>
       </c>
-      <c r="J15" s="53" t="s">
+      <c r="J15" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K15" s="53" t="s">
+      <c r="K15" s="44" t="s">
         <v>523</v>
       </c>
-      <c r="L15" s="53"/>
+      <c r="L15" s="44"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="52">
+      <c r="A16" s="43">
         <v>12</v>
       </c>
-      <c r="B16" s="52" t="s">
+      <c r="B16" s="43" t="s">
         <v>528</v>
       </c>
-      <c r="C16" s="52" t="s">
+      <c r="C16" s="43" t="s">
         <v>476</v>
       </c>
-      <c r="D16" s="53" t="s">
+      <c r="D16" s="44" t="s">
         <v>529</v>
       </c>
-      <c r="E16" s="52" t="s">
+      <c r="E16" s="43" t="s">
         <v>372</v>
       </c>
-      <c r="F16" s="53" t="s">
+      <c r="F16" s="44" t="s">
         <v>492</v>
       </c>
-      <c r="G16" s="53" t="s">
+      <c r="G16" s="44" t="s">
         <v>502</v>
       </c>
-      <c r="H16" s="53" t="s">
+      <c r="H16" s="44" t="s">
         <v>520</v>
       </c>
-      <c r="I16" s="52">
+      <c r="I16" s="43">
         <v>8.1</v>
       </c>
-      <c r="J16" s="53" t="s">
+      <c r="J16" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K16" s="53" t="s">
+      <c r="K16" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="L16" s="53"/>
+      <c r="L16" s="44"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="52">
+      <c r="A17" s="43">
         <v>13</v>
       </c>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="43" t="s">
         <v>530</v>
       </c>
-      <c r="C17" s="52" t="s">
+      <c r="C17" s="43" t="s">
         <v>531</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="D17" s="44" t="s">
         <v>532</v>
       </c>
-      <c r="E17" s="52" t="s">
+      <c r="E17" s="43" t="s">
         <v>415</v>
       </c>
-      <c r="F17" s="53" t="s">
+      <c r="F17" s="44" t="s">
         <v>533</v>
       </c>
-      <c r="G17" s="53" t="s">
+      <c r="G17" s="44" t="s">
         <v>479</v>
       </c>
-      <c r="H17" s="53" t="s">
+      <c r="H17" s="44" t="s">
         <v>509</v>
       </c>
-      <c r="I17" s="52">
+      <c r="I17" s="43">
         <v>5</v>
       </c>
-      <c r="J17" s="53" t="s">
+      <c r="J17" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K17" s="53" t="s">
+      <c r="K17" s="44" t="s">
         <v>534</v>
       </c>
-      <c r="L17" s="53"/>
+      <c r="L17" s="44"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="52">
+      <c r="A18" s="43">
         <v>14</v>
       </c>
-      <c r="B18" s="52" t="s">
+      <c r="B18" s="43" t="s">
         <v>535</v>
       </c>
-      <c r="C18" s="52" t="s">
+      <c r="C18" s="43" t="s">
         <v>531</v>
       </c>
-      <c r="D18" s="53" t="s">
+      <c r="D18" s="44" t="s">
         <v>536</v>
       </c>
-      <c r="E18" s="52" t="s">
+      <c r="E18" s="43" t="s">
         <v>372</v>
       </c>
-      <c r="F18" s="53" t="s">
+      <c r="F18" s="44" t="s">
         <v>537</v>
       </c>
-      <c r="G18" s="53" t="s">
+      <c r="G18" s="44" t="s">
         <v>502</v>
       </c>
-      <c r="H18" s="53" t="s">
+      <c r="H18" s="44" t="s">
         <v>503</v>
       </c>
-      <c r="I18" s="52">
+      <c r="I18" s="43">
         <v>17.600000000000001</v>
       </c>
-      <c r="J18" s="54" t="s">
+      <c r="J18" s="45" t="s">
         <v>494</v>
       </c>
-      <c r="K18" s="53" t="s">
+      <c r="K18" s="44" t="s">
         <v>488</v>
       </c>
-      <c r="L18" s="53" t="s">
+      <c r="L18" s="44" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="52">
+      <c r="A19" s="43">
         <v>15</v>
       </c>
-      <c r="B19" s="52" t="s">
+      <c r="B19" s="43" t="s">
         <v>538</v>
       </c>
-      <c r="C19" s="52" t="s">
+      <c r="C19" s="43" t="s">
         <v>531</v>
       </c>
-      <c r="D19" s="53" t="s">
+      <c r="D19" s="44" t="s">
         <v>539</v>
       </c>
-      <c r="E19" s="52" t="s">
+      <c r="E19" s="43" t="s">
         <v>424</v>
       </c>
-      <c r="F19" s="53" t="s">
+      <c r="F19" s="44" t="s">
         <v>540</v>
       </c>
-      <c r="G19" s="53" t="s">
+      <c r="G19" s="44" t="s">
         <v>485</v>
       </c>
-      <c r="H19" s="53" t="s">
+      <c r="H19" s="44" t="s">
         <v>503</v>
       </c>
-      <c r="I19" s="52">
+      <c r="I19" s="43">
         <v>9.1999999999999993</v>
       </c>
-      <c r="J19" s="53" t="s">
+      <c r="J19" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K19" s="53" t="s">
+      <c r="K19" s="44" t="s">
         <v>488</v>
       </c>
-      <c r="L19" s="53"/>
+      <c r="L19" s="44"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="52">
+      <c r="A20" s="43">
         <v>16</v>
       </c>
-      <c r="B20" s="52" t="s">
+      <c r="B20" s="43" t="s">
         <v>541</v>
       </c>
-      <c r="C20" s="52" t="s">
+      <c r="C20" s="43" t="s">
         <v>531</v>
       </c>
-      <c r="D20" s="53" t="s">
+      <c r="D20" s="44" t="s">
         <v>542</v>
       </c>
-      <c r="E20" s="52" t="s">
+      <c r="E20" s="43" t="s">
         <v>420</v>
       </c>
-      <c r="F20" s="53" t="s">
+      <c r="F20" s="44" t="s">
         <v>543</v>
       </c>
-      <c r="G20" s="53" t="s">
+      <c r="G20" s="44" t="s">
         <v>485</v>
       </c>
-      <c r="H20" s="53" t="s">
+      <c r="H20" s="44" t="s">
         <v>509</v>
       </c>
-      <c r="I20" s="52">
+      <c r="I20" s="43">
         <v>7.1</v>
       </c>
-      <c r="J20" s="53" t="s">
+      <c r="J20" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K20" s="53" t="s">
+      <c r="K20" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="L20" s="53"/>
+      <c r="L20" s="44"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="52">
+      <c r="A21" s="43">
         <v>17</v>
       </c>
-      <c r="B21" s="52" t="s">
+      <c r="B21" s="43" t="s">
         <v>544</v>
       </c>
-      <c r="C21" s="52" t="s">
+      <c r="C21" s="43" t="s">
         <v>531</v>
       </c>
-      <c r="D21" s="53" t="s">
+      <c r="D21" s="44" t="s">
         <v>545</v>
       </c>
-      <c r="E21" s="52" t="s">
+      <c r="E21" s="43" t="s">
         <v>420</v>
       </c>
-      <c r="F21" s="53" t="s">
+      <c r="F21" s="44" t="s">
         <v>507</v>
       </c>
-      <c r="G21" s="53" t="s">
+      <c r="G21" s="44" t="s">
         <v>502</v>
       </c>
-      <c r="H21" s="53" t="s">
+      <c r="H21" s="44" t="s">
         <v>546</v>
       </c>
-      <c r="I21" s="52">
+      <c r="I21" s="43">
         <v>11.8</v>
       </c>
-      <c r="J21" s="53" t="s">
+      <c r="J21" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K21" s="53" t="s">
+      <c r="K21" s="44" t="s">
         <v>488</v>
       </c>
-      <c r="L21" s="53"/>
+      <c r="L21" s="44"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="52">
+      <c r="A22" s="43">
         <v>18</v>
       </c>
-      <c r="B22" s="52" t="s">
+      <c r="B22" s="43" t="s">
         <v>547</v>
       </c>
-      <c r="C22" s="52" t="s">
+      <c r="C22" s="43" t="s">
         <v>531</v>
       </c>
-      <c r="D22" s="53" t="s">
+      <c r="D22" s="44" t="s">
         <v>548</v>
       </c>
-      <c r="E22" s="52" t="s">
+      <c r="E22" s="43" t="s">
         <v>424</v>
       </c>
-      <c r="F22" s="53" t="s">
+      <c r="F22" s="44" t="s">
         <v>478</v>
       </c>
-      <c r="G22" s="53" t="s">
+      <c r="G22" s="44" t="s">
         <v>485</v>
       </c>
-      <c r="H22" s="53" t="s">
+      <c r="H22" s="44" t="s">
         <v>486</v>
       </c>
-      <c r="I22" s="52">
+      <c r="I22" s="43">
         <v>16.100000000000001</v>
       </c>
-      <c r="J22" s="53" t="s">
+      <c r="J22" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K22" s="53" t="s">
+      <c r="K22" s="44" t="s">
         <v>498</v>
       </c>
-      <c r="L22" s="53"/>
+      <c r="L22" s="44"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="52">
+      <c r="A23" s="43">
         <v>19</v>
       </c>
-      <c r="B23" s="52" t="s">
+      <c r="B23" s="43" t="s">
         <v>549</v>
       </c>
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="43" t="s">
         <v>550</v>
       </c>
-      <c r="D23" s="53" t="s">
+      <c r="D23" s="44" t="s">
         <v>532</v>
       </c>
-      <c r="E23" s="52" t="s">
+      <c r="E23" s="43" t="s">
         <v>372</v>
       </c>
-      <c r="F23" s="53" t="s">
+      <c r="F23" s="44" t="s">
         <v>551</v>
       </c>
-      <c r="G23" s="53" t="s">
+      <c r="G23" s="44" t="s">
         <v>479</v>
       </c>
-      <c r="H23" s="53" t="s">
+      <c r="H23" s="44" t="s">
         <v>509</v>
       </c>
-      <c r="I23" s="52">
+      <c r="I23" s="43">
         <v>9.9</v>
       </c>
-      <c r="J23" s="54" t="s">
+      <c r="J23" s="45" t="s">
         <v>487</v>
       </c>
-      <c r="K23" s="53" t="s">
+      <c r="K23" s="44" t="s">
         <v>552</v>
       </c>
-      <c r="L23" s="53" t="s">
+      <c r="L23" s="44" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="52">
+      <c r="A24" s="43">
         <v>20</v>
       </c>
-      <c r="B24" s="52" t="s">
+      <c r="B24" s="43" t="s">
         <v>553</v>
       </c>
-      <c r="C24" s="52" t="s">
+      <c r="C24" s="43" t="s">
         <v>550</v>
       </c>
-      <c r="D24" s="53" t="s">
+      <c r="D24" s="44" t="s">
         <v>542</v>
       </c>
-      <c r="E24" s="52" t="s">
+      <c r="E24" s="43" t="s">
         <v>428</v>
       </c>
-      <c r="F24" s="53" t="s">
+      <c r="F24" s="44" t="s">
         <v>554</v>
       </c>
-      <c r="G24" s="53" t="s">
+      <c r="G24" s="44" t="s">
         <v>502</v>
       </c>
-      <c r="H24" s="53" t="s">
+      <c r="H24" s="44" t="s">
         <v>555</v>
       </c>
-      <c r="I24" s="52">
+      <c r="I24" s="43">
         <v>13.2</v>
       </c>
-      <c r="J24" s="53" t="s">
+      <c r="J24" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K24" s="53" t="s">
+      <c r="K24" s="44" t="s">
         <v>556</v>
       </c>
-      <c r="L24" s="53"/>
+      <c r="L24" s="44"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="52">
+      <c r="A25" s="43">
         <v>21</v>
       </c>
-      <c r="B25" s="52" t="s">
+      <c r="B25" s="43" t="s">
         <v>557</v>
       </c>
-      <c r="C25" s="52" t="s">
+      <c r="C25" s="43" t="s">
         <v>550</v>
       </c>
-      <c r="D25" s="53" t="s">
+      <c r="D25" s="44" t="s">
         <v>558</v>
       </c>
-      <c r="E25" s="52" t="s">
+      <c r="E25" s="43" t="s">
         <v>424</v>
       </c>
-      <c r="F25" s="53" t="s">
+      <c r="F25" s="44" t="s">
         <v>537</v>
       </c>
-      <c r="G25" s="53" t="s">
+      <c r="G25" s="44" t="s">
         <v>502</v>
       </c>
-      <c r="H25" s="53" t="s">
+      <c r="H25" s="44" t="s">
         <v>493</v>
       </c>
-      <c r="I25" s="52">
+      <c r="I25" s="43">
         <v>4.4000000000000004</v>
       </c>
-      <c r="J25" s="53" t="s">
+      <c r="J25" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K25" s="53" t="s">
+      <c r="K25" s="44" t="s">
         <v>498</v>
       </c>
-      <c r="L25" s="53"/>
+      <c r="L25" s="44"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="52">
+      <c r="A26" s="43">
         <v>22</v>
       </c>
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="43" t="s">
         <v>559</v>
       </c>
-      <c r="C26" s="52" t="s">
+      <c r="C26" s="43" t="s">
         <v>550</v>
       </c>
-      <c r="D26" s="53" t="s">
+      <c r="D26" s="44" t="s">
         <v>560</v>
       </c>
-      <c r="E26" s="52" t="s">
+      <c r="E26" s="43" t="s">
         <v>372</v>
       </c>
-      <c r="F26" s="53" t="s">
+      <c r="F26" s="44" t="s">
         <v>478</v>
       </c>
-      <c r="G26" s="53" t="s">
+      <c r="G26" s="44" t="s">
         <v>502</v>
       </c>
-      <c r="H26" s="53" t="s">
+      <c r="H26" s="44" t="s">
         <v>486</v>
       </c>
-      <c r="I26" s="52">
+      <c r="I26" s="43">
         <v>2.6</v>
       </c>
-      <c r="J26" s="53" t="s">
+      <c r="J26" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K26" s="53" t="s">
+      <c r="K26" s="44" t="s">
         <v>488</v>
       </c>
-      <c r="L26" s="53"/>
+      <c r="L26" s="44"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="52">
+      <c r="A27" s="43">
         <v>23</v>
       </c>
-      <c r="B27" s="52" t="s">
+      <c r="B27" s="43" t="s">
         <v>561</v>
       </c>
-      <c r="C27" s="52" t="s">
+      <c r="C27" s="43" t="s">
         <v>550</v>
       </c>
-      <c r="D27" s="53" t="s">
+      <c r="D27" s="44" t="s">
         <v>562</v>
       </c>
-      <c r="E27" s="52" t="s">
+      <c r="E27" s="43" t="s">
         <v>424</v>
       </c>
-      <c r="F27" s="53" t="s">
+      <c r="F27" s="44" t="s">
         <v>563</v>
       </c>
-      <c r="G27" s="53" t="s">
+      <c r="G27" s="44" t="s">
         <v>502</v>
       </c>
-      <c r="H27" s="53" t="s">
+      <c r="H27" s="44" t="s">
         <v>486</v>
       </c>
-      <c r="I27" s="52">
+      <c r="I27" s="43">
         <v>6.8</v>
       </c>
-      <c r="J27" s="53" t="s">
+      <c r="J27" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K27" s="53" t="s">
+      <c r="K27" s="44" t="s">
         <v>523</v>
       </c>
-      <c r="L27" s="53"/>
+      <c r="L27" s="44"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="52">
+      <c r="A28" s="43">
         <v>24</v>
       </c>
-      <c r="B28" s="52" t="s">
+      <c r="B28" s="43" t="s">
         <v>564</v>
       </c>
-      <c r="C28" s="52" t="s">
+      <c r="C28" s="43" t="s">
         <v>565</v>
       </c>
-      <c r="D28" s="53" t="s">
+      <c r="D28" s="44" t="s">
         <v>566</v>
       </c>
-      <c r="E28" s="52" t="s">
+      <c r="E28" s="43" t="s">
         <v>372</v>
       </c>
-      <c r="F28" s="53" t="s">
+      <c r="F28" s="44" t="s">
         <v>567</v>
       </c>
-      <c r="G28" s="53" t="s">
+      <c r="G28" s="44" t="s">
         <v>519</v>
       </c>
-      <c r="H28" s="53" t="s">
+      <c r="H28" s="44" t="s">
         <v>486</v>
       </c>
-      <c r="I28" s="52">
+      <c r="I28" s="43">
         <v>14.7</v>
       </c>
-      <c r="J28" s="54" t="s">
+      <c r="J28" s="45" t="s">
         <v>494</v>
       </c>
-      <c r="K28" s="53" t="s">
+      <c r="K28" s="44" t="s">
         <v>534</v>
       </c>
-      <c r="L28" s="53" t="s">
+      <c r="L28" s="44" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="52">
+      <c r="A29" s="43">
         <v>25</v>
       </c>
-      <c r="B29" s="52" t="s">
+      <c r="B29" s="43" t="s">
         <v>568</v>
       </c>
-      <c r="C29" s="52" t="s">
+      <c r="C29" s="43" t="s">
         <v>565</v>
       </c>
-      <c r="D29" s="53" t="s">
+      <c r="D29" s="44" t="s">
         <v>569</v>
       </c>
-      <c r="E29" s="52" t="s">
+      <c r="E29" s="43" t="s">
         <v>428</v>
       </c>
-      <c r="F29" s="53" t="s">
+      <c r="F29" s="44" t="s">
         <v>501</v>
       </c>
-      <c r="G29" s="53" t="s">
+      <c r="G29" s="44" t="s">
         <v>519</v>
       </c>
-      <c r="H29" s="53" t="s">
+      <c r="H29" s="44" t="s">
         <v>520</v>
       </c>
-      <c r="I29" s="52">
+      <c r="I29" s="43">
         <v>9.6999999999999993</v>
       </c>
-      <c r="J29" s="53" t="s">
+      <c r="J29" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K29" s="53" t="s">
+      <c r="K29" s="44" t="s">
         <v>488</v>
       </c>
-      <c r="L29" s="53"/>
+      <c r="L29" s="44"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="52">
+      <c r="A30" s="43">
         <v>26</v>
       </c>
-      <c r="B30" s="52" t="s">
+      <c r="B30" s="43" t="s">
         <v>570</v>
       </c>
-      <c r="C30" s="52" t="s">
+      <c r="C30" s="43" t="s">
         <v>565</v>
       </c>
-      <c r="D30" s="53" t="s">
+      <c r="D30" s="44" t="s">
         <v>571</v>
       </c>
-      <c r="E30" s="52" t="s">
+      <c r="E30" s="43" t="s">
         <v>424</v>
       </c>
-      <c r="F30" s="53" t="s">
+      <c r="F30" s="44" t="s">
         <v>533</v>
       </c>
-      <c r="G30" s="53" t="s">
+      <c r="G30" s="44" t="s">
         <v>479</v>
       </c>
-      <c r="H30" s="53" t="s">
+      <c r="H30" s="44" t="s">
         <v>486</v>
       </c>
-      <c r="I30" s="52">
+      <c r="I30" s="43">
         <v>5.4</v>
       </c>
-      <c r="J30" s="53" t="s">
+      <c r="J30" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K30" s="53" t="s">
+      <c r="K30" s="44" t="s">
         <v>552</v>
       </c>
-      <c r="L30" s="53"/>
+      <c r="L30" s="44"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="52">
+      <c r="A31" s="43">
         <v>27</v>
       </c>
-      <c r="B31" s="52" t="s">
+      <c r="B31" s="43" t="s">
         <v>572</v>
       </c>
-      <c r="C31" s="52" t="s">
+      <c r="C31" s="43" t="s">
         <v>565</v>
       </c>
-      <c r="D31" s="53" t="s">
+      <c r="D31" s="44" t="s">
         <v>573</v>
       </c>
-      <c r="E31" s="52" t="s">
+      <c r="E31" s="43" t="s">
         <v>428</v>
       </c>
-      <c r="F31" s="53" t="s">
+      <c r="F31" s="44" t="s">
         <v>478</v>
       </c>
-      <c r="G31" s="53" t="s">
+      <c r="G31" s="44" t="s">
         <v>485</v>
       </c>
-      <c r="H31" s="53" t="s">
+      <c r="H31" s="44" t="s">
         <v>493</v>
       </c>
-      <c r="I31" s="52">
+      <c r="I31" s="43">
         <v>15</v>
       </c>
-      <c r="J31" s="54" t="s">
+      <c r="J31" s="45" t="s">
         <v>494</v>
       </c>
-      <c r="K31" s="53" t="s">
+      <c r="K31" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="L31" s="53" t="s">
+      <c r="L31" s="44" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="52">
+      <c r="A32" s="43">
         <v>28</v>
       </c>
-      <c r="B32" s="52" t="s">
+      <c r="B32" s="43" t="s">
         <v>574</v>
       </c>
-      <c r="C32" s="52" t="s">
+      <c r="C32" s="43" t="s">
         <v>575</v>
       </c>
-      <c r="D32" s="53" t="s">
+      <c r="D32" s="44" t="s">
         <v>571</v>
       </c>
-      <c r="E32" s="52" t="s">
+      <c r="E32" s="43" t="s">
         <v>372</v>
       </c>
-      <c r="F32" s="53" t="s">
+      <c r="F32" s="44" t="s">
         <v>484</v>
       </c>
-      <c r="G32" s="53" t="s">
+      <c r="G32" s="44" t="s">
         <v>485</v>
       </c>
-      <c r="H32" s="53" t="s">
+      <c r="H32" s="44" t="s">
         <v>486</v>
       </c>
-      <c r="I32" s="52">
+      <c r="I32" s="43">
         <v>5.0999999999999996</v>
       </c>
-      <c r="J32" s="53" t="s">
+      <c r="J32" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K32" s="53" t="s">
+      <c r="K32" s="44" t="s">
         <v>504</v>
       </c>
-      <c r="L32" s="53"/>
+      <c r="L32" s="44"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="52">
+      <c r="A33" s="43">
         <v>29</v>
       </c>
-      <c r="B33" s="52" t="s">
+      <c r="B33" s="43" t="s">
         <v>576</v>
       </c>
-      <c r="C33" s="52" t="s">
+      <c r="C33" s="43" t="s">
         <v>575</v>
       </c>
-      <c r="D33" s="53" t="s">
+      <c r="D33" s="44" t="s">
         <v>577</v>
       </c>
-      <c r="E33" s="52" t="s">
+      <c r="E33" s="43" t="s">
         <v>420</v>
       </c>
-      <c r="F33" s="53" t="s">
+      <c r="F33" s="44" t="s">
         <v>526</v>
       </c>
-      <c r="G33" s="53" t="s">
+      <c r="G33" s="44" t="s">
         <v>485</v>
       </c>
-      <c r="H33" s="53" t="s">
+      <c r="H33" s="44" t="s">
         <v>520</v>
       </c>
-      <c r="I33" s="52">
+      <c r="I33" s="43">
         <v>6.6</v>
       </c>
-      <c r="J33" s="54" t="s">
+      <c r="J33" s="45" t="s">
         <v>494</v>
       </c>
-      <c r="K33" s="53" t="s">
+      <c r="K33" s="44" t="s">
         <v>504</v>
       </c>
-      <c r="L33" s="53" t="s">
+      <c r="L33" s="44" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="52">
+      <c r="A34" s="43">
         <v>30</v>
       </c>
-      <c r="B34" s="52" t="s">
+      <c r="B34" s="43" t="s">
         <v>578</v>
       </c>
-      <c r="C34" s="52" t="s">
+      <c r="C34" s="43" t="s">
         <v>579</v>
       </c>
-      <c r="D34" s="53" t="s">
+      <c r="D34" s="44" t="s">
         <v>580</v>
       </c>
-      <c r="E34" s="52" t="s">
+      <c r="E34" s="43" t="s">
         <v>372</v>
       </c>
-      <c r="F34" s="53" t="s">
+      <c r="F34" s="44" t="s">
         <v>581</v>
       </c>
-      <c r="G34" s="53" t="s">
+      <c r="G34" s="44" t="s">
         <v>479</v>
       </c>
-      <c r="H34" s="53" t="s">
+      <c r="H34" s="44" t="s">
         <v>486</v>
       </c>
-      <c r="I34" s="52">
+      <c r="I34" s="43">
         <v>7.1</v>
       </c>
-      <c r="J34" s="53" t="s">
+      <c r="J34" s="44" t="s">
         <v>481</v>
       </c>
-      <c r="K34" s="53" t="s">
+      <c r="K34" s="44" t="s">
         <v>582</v>
       </c>
-      <c r="L34" s="53"/>
+      <c r="L34" s="44"/>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="54" t="s">
         <v>583</v>
       </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
+      <c r="B36" s="54"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="54"/>
+      <c r="K36" s="54"/>
+      <c r="L36" s="54"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
+      <c r="A37" s="54"/>
+      <c r="B37" s="54"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="54"/>
+      <c r="I37" s="54"/>
+      <c r="J37" s="54"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5524,561 +5524,561 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
     </row>
     <row r="5" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
+      <c r="A6" s="3">
         <v>1</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="3">
         <v>36</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="3">
         <v>28</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="3">
         <v>22</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="3">
         <v>4</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="3">
         <v>2</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="4">
         <f>IF(D6=0,0,E6/D6)</f>
         <v>0.7857142857142857</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="3">
         <f>C6-D6</f>
         <v>8</v>
       </c>
-      <c r="J6" s="32" t="s">
+      <c r="J6" s="23" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
+      <c r="A7" s="3">
         <v>2</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="3">
         <v>4</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="3">
         <v>3</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="3">
         <v>2</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="3">
         <v>0</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="3">
         <v>1</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="4">
         <f>IF(D7=0,0,E7/D7)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="3">
         <f>C7-D7</f>
         <v>1</v>
       </c>
-      <c r="J7" s="32" t="s">
+      <c r="J7" s="23" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
+      <c r="A8" s="3">
         <v>3</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="3">
         <v>4</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="3">
         <v>3</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="3">
         <v>3</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="3">
         <v>0</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="3">
         <v>0</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="4">
         <f>IF(D8=0,0,E8/D8)</f>
         <v>1</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="3">
         <f>C8-D8</f>
         <v>1</v>
       </c>
-      <c r="J8" s="32" t="s">
+      <c r="J8" s="23" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
-      <c r="B9" s="27" t="s">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="18">
         <f>SUM(C6:C8)</f>
         <v>44</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="18">
         <f>SUM(D6:D8)</f>
         <v>34</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="18">
         <f>SUM(E6:E8)</f>
         <v>27</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="18">
         <f>SUM(F6:F8)</f>
         <v>4</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="18">
         <f>SUM(G6:G8)</f>
         <v>3</v>
       </c>
-      <c r="H9" s="33">
+      <c r="H9" s="24">
         <f>IF(D9=0,0,E9/D9)</f>
         <v>0.79411764705882348</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="18">
         <f>C9-D9</f>
         <v>10</v>
       </c>
-      <c r="J9" s="27"/>
+      <c r="J9" s="18"/>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="49"/>
     </row>
     <row r="12" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="12">
+      <c r="A13" s="3">
         <v>1</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="3">
         <v>15</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="3">
         <v>12</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="3">
         <v>9</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="3">
         <v>2</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="3">
         <v>1</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="4">
         <f t="shared" ref="H13:H19" si="0">IF(D13=0,0,E13/D13)</f>
         <v>0.75</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="3">
         <f t="shared" ref="I13:I19" si="1">C13-D13</f>
         <v>3</v>
       </c>
-      <c r="J13" s="32" t="s">
+      <c r="J13" s="23" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="12">
+      <c r="A14" s="3">
         <v>2</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="3">
         <v>10</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="3">
         <v>8</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="3">
         <v>7</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="3">
         <v>1</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="4">
         <f t="shared" si="0"/>
         <v>0.875</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="3">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J14" s="32" t="s">
+      <c r="J14" s="23" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="12">
+      <c r="A15" s="3">
         <v>3</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="3">
         <v>18</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="3">
         <v>14</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="3">
         <v>11</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="3">
         <v>2</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="3">
         <v>1</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="4">
         <f t="shared" si="0"/>
         <v>0.7857142857142857</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="J15" s="32" t="s">
+      <c r="J15" s="23" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="12">
+      <c r="A16" s="3">
         <v>4</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="3">
         <v>4</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="3">
         <v>3</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="3">
         <v>3</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="3">
         <v>0</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="3">
         <v>0</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="3">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J16" s="32" t="s">
+      <c r="J16" s="23" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="12">
+      <c r="A17" s="3">
         <v>5</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="3">
         <v>5</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="3">
         <v>4</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="3">
         <v>3</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="3">
         <v>1</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="3">
         <v>0</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="4">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="3">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J17" s="32" t="s">
+      <c r="J17" s="23" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="12">
+      <c r="A18" s="3">
         <v>6</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="3">
         <v>12</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="3">
         <v>9</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="3">
         <v>8</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="3">
         <v>1</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="3">
         <v>0</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="4">
         <f t="shared" si="0"/>
         <v>0.88888888888888884</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="3">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J18" s="32" t="s">
+      <c r="J18" s="23" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="27"/>
-      <c r="B19" s="27" t="s">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="18">
         <f>SUM(C13:C18)</f>
         <v>64</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="18">
         <f>SUM(D13:D18)</f>
         <v>50</v>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="18">
         <f>SUM(E13:E18)</f>
         <v>41</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="18">
         <f>SUM(F13:F18)</f>
         <v>7</v>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="18">
         <f>SUM(G13:G18)</f>
         <v>2</v>
       </c>
-      <c r="H19" s="33">
+      <c r="H19" s="24">
         <f t="shared" si="0"/>
         <v>0.82</v>
       </c>
-      <c r="I19" s="27">
+      <c r="I19" s="18">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="J19" s="27"/>
+      <c r="J19" s="18"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="34"/>
-      <c r="B21" s="34" t="s">
+      <c r="A21" s="25"/>
+      <c r="B21" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="25">
         <f>C9+C19</f>
         <v>108</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="25">
         <f>D9+D19</f>
         <v>84</v>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="25">
         <f>E9+E19</f>
         <v>68</v>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="25">
         <f>F9+F19</f>
         <v>11</v>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="25">
         <f>G9+G19</f>
         <v>5</v>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="26">
         <f>IF(D21=0,0,E21/D21)</f>
         <v>0.80952380952380953</v>
       </c>
-      <c r="I21" s="34">
+      <c r="I21" s="25">
         <f>C21-D21</f>
         <v>24</v>
       </c>
-      <c r="J21" s="34"/>
+      <c r="J21" s="25"/>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="48"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
+      <c r="A24" s="48"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6112,559 +6112,559 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
     </row>
     <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="3">
         <v>520</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="3">
         <v>485</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="3">
         <f t="shared" ref="E5:E16" si="0">C5-D5</f>
         <v>35</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="4">
         <f t="shared" ref="F5:F16" si="1">IF(C5=0,0,D5/C5)</f>
         <v>0.93269230769230771</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="3">
         <v>410</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="3">
         <v>45</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="3">
         <v>20</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="3">
         <v>8</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="3">
         <v>85</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="3">
         <v>78</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="4">
         <f t="shared" si="1"/>
         <v>0.91764705882352937</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="3">
         <v>65</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="3">
         <v>8</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="3">
         <v>3</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="3">
         <v>2</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="3">
         <v>48</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="3">
         <v>42</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="4">
         <f t="shared" si="1"/>
         <v>0.875</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="3">
         <v>35</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="3">
         <v>4</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="3">
         <v>2</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="3">
         <v>1</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="3">
         <v>18</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="3">
         <v>15</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="4">
         <f t="shared" si="1"/>
         <v>0.83333333333333337</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="3">
         <v>12</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="3">
         <v>2</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="3">
         <v>1</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="3">
         <v>0</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="3">
         <v>65</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="3">
         <v>60</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="4">
         <f t="shared" si="1"/>
         <v>0.92307692307692313</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="3">
         <v>55</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="3">
         <v>3</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="3">
         <v>2</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="3">
         <v>0</v>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="12">
+      <c r="A10" s="3">
         <v>6</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="3">
         <v>36</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="3">
         <v>32</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="4">
         <f t="shared" si="1"/>
         <v>0.88888888888888884</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="3">
         <v>28</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="3">
         <v>2</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="3">
         <v>1</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="3">
         <v>1</v>
       </c>
-      <c r="K10" s="12">
+      <c r="K10" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="12">
+      <c r="A11" s="3">
         <v>7</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="3">
         <v>12</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="3">
         <v>10</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="4">
         <f t="shared" si="1"/>
         <v>0.83333333333333337</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="3">
         <v>9</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="3">
         <v>1</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="3">
         <v>0</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="3">
         <v>0</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="12">
+      <c r="A12" s="3">
         <v>8</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="3">
         <v>8</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="3">
         <v>7</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="4">
         <f t="shared" si="1"/>
         <v>0.875</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="3">
         <v>6</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="3">
         <v>1</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="3">
         <v>0</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="3">
         <v>0</v>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="12">
+      <c r="A13" s="3">
         <v>9</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="3">
         <v>12</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="3">
         <v>10</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="4">
         <f t="shared" si="1"/>
         <v>0.83333333333333337</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="3">
         <v>8</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="3">
         <v>1</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="3">
         <v>1</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="12">
+      <c r="A14" s="3">
         <v>10</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="3">
         <v>8</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="3">
         <v>6</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="4">
         <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="3">
         <v>5</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="3">
         <v>1</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="12">
+      <c r="A15" s="3">
         <v>11</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="3">
         <v>25</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="3">
         <v>22</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="4">
         <f t="shared" si="1"/>
         <v>0.88</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="3">
         <v>20</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="3">
         <v>2</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="3">
         <v>0</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="27"/>
-      <c r="B16" s="27" t="s">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="18">
         <f>SUM(C5:C15)</f>
         <v>837</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="18">
         <f>SUM(D5:D15)</f>
         <v>767</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="18">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="24">
         <f t="shared" si="1"/>
         <v>0.91636798088410987</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="18">
         <f>SUM(G5:G15)</f>
         <v>653</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="18">
         <f>SUM(H5:H15)</f>
         <v>70</v>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="18">
         <f>SUM(I5:I15)</f>
         <v>30</v>
       </c>
-      <c r="J16" s="27">
+      <c r="J16" s="18">
         <f>SUM(J5:J15)</f>
         <v>12</v>
       </c>
-      <c r="K16" s="27">
+      <c r="K16" s="18">
         <f>SUM(K5:K15)</f>
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="51" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
+      <c r="A20" s="51"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6696,358 +6696,358 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="4" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="3">
         <v>24</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="3">
         <v>18</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="3">
         <v>15</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="3">
         <v>3</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="4">
         <f t="shared" ref="G5:G14" si="0">IF(C5=0,0,D5/C5)</f>
         <v>0.75</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="4">
         <f t="shared" ref="H5:H14" si="1">IF(D5=0,0,E5/D5)</f>
         <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="3">
         <v>18</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="3">
         <v>14</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="3">
         <v>12</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="3">
         <v>2</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="4">
         <f t="shared" si="0"/>
         <v>0.77777777777777779</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="4">
         <f t="shared" si="1"/>
         <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="3">
         <v>30</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="3">
         <v>25</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="3">
         <v>22</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="3">
         <v>3</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="4">
         <f t="shared" si="0"/>
         <v>0.83333333333333337</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="4">
         <f t="shared" si="1"/>
         <v>0.88</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="3">
         <v>12</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="3">
         <v>9</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="3">
         <v>7</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="3">
         <v>2</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="4">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="4">
         <f t="shared" si="1"/>
         <v>0.77777777777777779</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="3">
         <v>16</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="3">
         <v>13</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="3">
         <v>12</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="3">
         <v>1</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="4">
         <f t="shared" si="0"/>
         <v>0.8125</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="4">
         <f t="shared" si="1"/>
         <v>0.92307692307692313</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="12">
+      <c r="A10" s="3">
         <v>6</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="3">
         <v>20</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="3">
         <v>16</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="3">
         <v>14</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="3">
         <v>2</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="4">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="4">
         <f t="shared" si="1"/>
         <v>0.875</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="12">
+      <c r="A11" s="3">
         <v>7</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="3">
         <v>45</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="3">
         <v>40</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="3">
         <v>38</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="3">
         <v>2</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="4">
         <f t="shared" si="0"/>
         <v>0.88888888888888884</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="4">
         <f t="shared" si="1"/>
         <v>0.95</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="12">
+      <c r="A12" s="3">
         <v>8</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="3">
         <v>55</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="3">
         <v>50</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="3">
         <v>48</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="3">
         <v>2</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="4">
         <f t="shared" si="0"/>
         <v>0.90909090909090906</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="4">
         <f t="shared" si="1"/>
         <v>0.96</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="12">
+      <c r="A13" s="3">
         <v>9</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="3">
         <v>28</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="3">
         <v>22</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="3">
         <v>20</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="3">
         <v>2</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="4">
         <f t="shared" si="0"/>
         <v>0.7857142857142857</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="4">
         <f t="shared" si="1"/>
         <v>0.90909090909090906</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="27"/>
-      <c r="B14" s="27" t="s">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="18">
         <f>SUM(C5:C13)</f>
         <v>248</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="18">
         <f>SUM(D5:D13)</f>
         <v>207</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="18">
         <f>SUM(E5:E13)</f>
         <v>188</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="18">
         <f>SUM(F5:F13)</f>
         <v>19</v>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="24">
         <f t="shared" si="0"/>
         <v>0.83467741935483875</v>
       </c>
-      <c r="H14" s="33">
+      <c r="H14" s="24">
         <f t="shared" si="1"/>
         <v>0.90821256038647347</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="A17" s="52"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7079,246 +7079,246 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="4" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="3">
         <v>28</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="3">
         <v>24</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="3">
         <v>21</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="3">
         <v>3</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="4">
         <f t="shared" ref="G5:H10" si="0">IF(C5=0,0,D5/C5)</f>
         <v>0.8571428571428571</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="4">
         <f t="shared" si="0"/>
         <v>0.875</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="3">
         <v>35</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="3">
         <v>30</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="3">
         <v>28</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="3">
         <v>2</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="4">
         <f t="shared" si="0"/>
         <v>0.8571428571428571</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="4">
         <f t="shared" si="0"/>
         <v>0.93333333333333335</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="3">
         <v>18</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="3">
         <v>15</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="3">
         <v>14</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="3">
         <v>1</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="4">
         <f t="shared" si="0"/>
         <v>0.83333333333333337</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="4">
         <f t="shared" si="0"/>
         <v>0.93333333333333335</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="3">
         <v>8</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="3">
         <v>6</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="3">
         <v>5</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="3">
         <v>1</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="4">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="4">
         <f t="shared" si="0"/>
         <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="3">
         <v>6</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="3">
         <v>5</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="3">
         <v>4</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="3">
         <v>1</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="4">
         <f t="shared" si="0"/>
         <v>0.83333333333333337</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="4">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27" t="s">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="18">
         <f>SUM(C5:C9)</f>
         <v>95</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="18">
         <f>SUM(D5:D9)</f>
         <v>80</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="18">
         <f>SUM(E5:E9)</f>
         <v>72</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="18">
         <f>SUM(F5:F9)</f>
         <v>8</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="24">
         <f t="shared" si="0"/>
         <v>0.84210526315789469</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10" s="24">
         <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="52" t="s">
         <v>124</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="A13" s="52"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7348,406 +7348,406 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
     </row>
     <row r="5" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="1" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
+      <c r="A6" s="3">
         <v>1</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="27">
         <v>180000</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="27">
         <v>152000</v>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="27">
         <f>C6-D6</f>
         <v>28000</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="4">
         <f>IF(C6=0,0,D6/C6)</f>
         <v>0.84444444444444444</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="27">
         <v>95000</v>
       </c>
-      <c r="H6" s="36">
+      <c r="H6" s="27">
         <v>57000</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
+      <c r="A7" s="3">
         <v>2</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="27">
         <v>25000</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="27">
         <v>21000</v>
       </c>
-      <c r="E7" s="36">
+      <c r="E7" s="27">
         <f>C7-D7</f>
         <v>4000</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="4">
         <f>IF(C7=0,0,D7/C7)</f>
         <v>0.84</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="27">
         <v>14000</v>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="27">
         <v>7000</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
+      <c r="A8" s="3">
         <v>3</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="27">
         <v>45000</v>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="27">
         <v>38000</v>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="27">
         <f>C8-D8</f>
         <v>7000</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="4">
         <f>IF(C8=0,0,D8/C8)</f>
         <v>0.84444444444444444</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="27">
         <v>25000</v>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="27">
         <v>13000</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
+      <c r="A9" s="3">
         <v>4</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="27">
         <v>18000</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="27">
         <v>14500</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="27">
         <f>C9-D9</f>
         <v>3500</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="4">
         <f>IF(C9=0,0,D9/C9)</f>
         <v>0.80555555555555558</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="27">
         <v>9000</v>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="27">
         <v>5500</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
     </row>
     <row r="12" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="1" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="12">
+      <c r="A13" s="3">
         <v>1</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="27">
         <v>420</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="27">
         <v>360</v>
       </c>
-      <c r="E13" s="36">
+      <c r="E13" s="27">
         <f t="shared" ref="E13:E18" si="0">C13-D13</f>
         <v>60</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="4">
         <f t="shared" ref="F13:F18" si="1">IF(C13=0,0,D13/C13)</f>
         <v>0.8571428571428571</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="27">
         <v>220</v>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="27">
         <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="12">
+      <c r="A14" s="3">
         <v>2</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="27">
         <v>800</v>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="27">
         <v>680</v>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="27">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="4">
         <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="27">
         <v>400</v>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="27">
         <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="12">
+      <c r="A15" s="3">
         <v>3</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="27">
         <v>650</v>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="27">
         <v>520</v>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="27">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="4">
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="27">
         <v>300</v>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="27">
         <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="12">
+      <c r="A16" s="3">
         <v>4</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="27">
         <v>36</v>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="27">
         <v>28</v>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="27">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="4">
         <f t="shared" si="1"/>
         <v>0.77777777777777779</v>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="27">
         <v>16</v>
       </c>
-      <c r="H16" s="36">
+      <c r="H16" s="27">
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="12">
+      <c r="A17" s="3">
         <v>5</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="36">
+      <c r="C17" s="27">
         <v>1200</v>
       </c>
-      <c r="D17" s="36">
+      <c r="D17" s="27">
         <v>980</v>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="27">
         <f t="shared" si="0"/>
         <v>220</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="4">
         <f t="shared" si="1"/>
         <v>0.81666666666666665</v>
       </c>
-      <c r="G17" s="36">
+      <c r="G17" s="27">
         <v>600</v>
       </c>
-      <c r="H17" s="36">
+      <c r="H17" s="27">
         <v>380</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="12">
+      <c r="A18" s="3">
         <v>6</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="27">
         <v>450</v>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="27">
         <v>380</v>
       </c>
-      <c r="E18" s="36">
+      <c r="E18" s="27">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="4">
         <f t="shared" si="1"/>
         <v>0.84444444444444444</v>
       </c>
-      <c r="G18" s="36">
+      <c r="G18" s="27">
         <v>250</v>
       </c>
-      <c r="H18" s="36">
+      <c r="H18" s="27">
         <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
+      <c r="A21" s="53"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7778,152 +7778,152 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="47" t="s">
         <v>144</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="4" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="27">
         <v>1850</v>
       </c>
-      <c r="D5" s="36">
-        <v>22000</v>
-      </c>
-      <c r="E5" s="36">
+      <c r="D5" s="27">
+        <v>2200</v>
+      </c>
+      <c r="E5" s="27">
         <f>D5-C5</f>
-        <v>20150</v>
-      </c>
-      <c r="F5" s="32" t="s">
+        <v>350</v>
+      </c>
+      <c r="F5" s="23" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="27">
         <v>1250</v>
       </c>
-      <c r="D6" s="36">
-        <v>15000</v>
-      </c>
-      <c r="E6" s="36">
+      <c r="D6" s="27">
+        <v>1500</v>
+      </c>
+      <c r="E6" s="27">
         <f>D6-C6</f>
-        <v>13750</v>
-      </c>
-      <c r="F6" s="32" t="s">
+        <v>250</v>
+      </c>
+      <c r="F6" s="23" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="27">
         <v>820</v>
       </c>
-      <c r="D7" s="36">
-        <v>10000</v>
-      </c>
-      <c r="E7" s="36">
+      <c r="D7" s="27">
+        <v>1000</v>
+      </c>
+      <c r="E7" s="27">
         <f>D7-C7</f>
-        <v>9180</v>
-      </c>
-      <c r="F7" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="F7" s="23" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27" t="s">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="28">
         <f>SUM(C5:C7)</f>
         <v>3920</v>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="28">
         <f>SUM(D5:D7)</f>
-        <v>47000</v>
-      </c>
-      <c r="E8" s="37">
+        <v>4700</v>
+      </c>
+      <c r="E8" s="28">
         <f>D8-C8</f>
-        <v>43080</v>
-      </c>
-      <c r="F8" s="27"/>
+        <v>780</v>
+      </c>
+      <c r="F8" s="18"/>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="48" t="s">
         <v>155</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="A12" s="48"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7954,155 +7954,155 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="46" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
     </row>
     <row r="4" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="38">
+      <c r="A5" s="29">
         <v>1</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="C5" s="38">
+      <c r="C5" s="29">
         <v>3</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="E5" s="40">
+      <c r="E5" s="31">
         <v>1250000</v>
       </c>
-      <c r="F5" s="39" t="s">
+      <c r="F5" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="G5" s="39" t="s">
+      <c r="G5" s="30" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="41">
+      <c r="A6" s="32">
         <v>2</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="33" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="41">
+      <c r="C6" s="32">
         <v>7</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="34">
         <v>185000</v>
       </c>
-      <c r="F6" s="42" t="s">
+      <c r="F6" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="G6" s="42" t="s">
+      <c r="G6" s="33" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="44">
+      <c r="A7" s="35">
         <v>3</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="C7" s="44">
+      <c r="C7" s="35">
         <v>12</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="35" t="s">
         <v>170</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="37">
         <v>45000</v>
       </c>
-      <c r="F7" s="45" t="s">
+      <c r="F7" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="G7" s="45" t="s">
+      <c r="G7" s="36" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27" t="s">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="18">
         <f>SUM(C5:C7)</f>
         <v>22</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="37">
+      <c r="D8" s="18"/>
+      <c r="E8" s="28">
         <f>SUM(E5:E7)</f>
         <v>1480000</v>
       </c>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="A11" s="52"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8133,299 +8133,299 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="46" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="1" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="23" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="47">
+      <c r="A6" s="38">
         <v>2</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="39" t="s">
         <v>191</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="F6" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="G6" s="48" t="s">
+      <c r="G6" s="39" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="23" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="23" t="s">
         <v>203</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="23" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="E9" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="23" t="s">
         <v>210</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="23" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="41">
+      <c r="A10" s="32">
         <v>6</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="32" t="s">
         <v>213</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="D10" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="E10" s="42" t="s">
+      <c r="E10" s="33" t="s">
         <v>215</v>
       </c>
-      <c r="F10" s="42" t="s">
+      <c r="F10" s="33" t="s">
         <v>216</v>
       </c>
-      <c r="G10" s="42" t="s">
+      <c r="G10" s="33" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="47">
+      <c r="A11" s="38">
         <v>7</v>
       </c>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="39" t="s">
         <v>218</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="D11" s="47" t="s">
+      <c r="D11" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="E11" s="48" t="s">
+      <c r="E11" s="39" t="s">
         <v>220</v>
       </c>
-      <c r="F11" s="48" t="s">
+      <c r="F11" s="39" t="s">
         <v>221</v>
       </c>
-      <c r="G11" s="48" t="s">
+      <c r="G11" s="39" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="12">
+      <c r="A12" s="3">
         <v>8</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="F12" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="23" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="41">
+      <c r="A13" s="32">
         <v>9</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="33" t="s">
         <v>229</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="32" t="s">
         <v>213</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="D13" s="32" t="s">
         <v>230</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="33" t="s">
         <v>231</v>
       </c>
-      <c r="F13" s="42" t="s">
+      <c r="F13" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="G13" s="42" t="s">
+      <c r="G13" s="33" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="12">
+      <c r="A14" s="3">
         <v>10</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="23" t="s">
         <v>236</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="23" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="52"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+      <c r="A17" s="52"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Smart Dashboard - 19 Punjab.xlsx
+++ b/Smart Dashboard - 19 Punjab.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2B0D31-BC4C-48E1-892E-95FEE06DC4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Combat Potential" sheetId="1" r:id="rId1"/>
